--- a/Collections/EURO/Cyprus/#EURO#Cyprus#Regular#[2008-present]#circulation_qualitys.xlsx
+++ b/Collections/EURO/Cyprus/#EURO#Cyprus#Regular#[2008-present]#circulation_qualitys.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Cyprus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792FD865-2508-4E86-B7CB-9FE9FF3A0CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15391FE2-8B4D-46A9-88CE-D082FDB68D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -652,7 +655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="89">
   <si>
     <t>-</t>
   </si>
@@ -1294,7 +1297,271 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="68">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1591,9 +1858,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="34" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1862,7 +2129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2365,6 +2632,64 @@
         <v/>
       </c>
     </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" ref="I19:I20" si="4">IF(OR(AND(G19&gt;1,G19&lt;&gt;"-"),AND(H19&gt;1,H19&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="4">
@@ -2375,12 +2700,12 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G3:G18">
-    <cfRule type="containsText" dxfId="34" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G18">
-    <cfRule type="colorScale" priority="28">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2392,11 +2717,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H18">
-    <cfRule type="containsText" dxfId="33" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H18">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="32" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2408,6 +2750,57 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="28" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -2416,7 +2809,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2859,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="str">
-        <f t="shared" ref="I16:I18" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I16:I20" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2915,6 +3308,64 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2929,11 +3380,60 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G3:G18">
-    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G18">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H14 H16 H18">
+    <cfRule type="containsText" dxfId="64" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H14 H16 H18">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H4">
+    <cfRule type="containsText" dxfId="63" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
+    <cfRule type="containsText" dxfId="62" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2945,27 +3445,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H14 H16 H18">
-    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H14 H16 H18">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H4">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2977,12 +3462,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15 H17">
-    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17 H15">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="26" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2994,6 +3496,23 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -3002,7 +3521,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3445,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="str">
-        <f t="shared" ref="I16:I18" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I16:I20" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3501,6 +4020,64 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3515,11 +4092,60 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G3:G14 G16 G18">
-    <cfRule type="containsText" dxfId="28" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G14 G16 G18">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H14 H16 H18">
+    <cfRule type="containsText" dxfId="60" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H14 H16 H18">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H4">
+    <cfRule type="containsText" dxfId="59" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
+    <cfRule type="containsText" dxfId="58" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3531,27 +4157,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H14 H16 H18">
-    <cfRule type="containsText" dxfId="27" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H14 H16 H18">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H4">
-    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="G15 G17">
+    <cfRule type="containsText" dxfId="57" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15 G17">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3563,12 +4174,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15 H17">
-    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17 H15">
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="23" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="22" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3580,12 +4208,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15 G17">
-    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17 G15">
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3605,7 +4250,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4076,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="str">
-        <f t="shared" ref="I16:I18" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I16:I20" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4136,6 +4781,66 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4150,11 +4855,77 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G14 G16 G18">
-    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G14 G16 G18">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H14 H16 H18">
+    <cfRule type="containsText" dxfId="55" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H14 H16 H18">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H4">
+    <cfRule type="containsText" dxfId="54" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15 G17">
+    <cfRule type="containsText" dxfId="53" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15 G17">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
+    <cfRule type="containsText" dxfId="52" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4166,12 +4937,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H14 H16 H18">
-    <cfRule type="containsText" dxfId="22" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H14 H16 H18">
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4183,10 +4954,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H4">
-    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4198,12 +4971,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15 G17">
-    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17 G15">
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4215,12 +4988,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15 H17">
-    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17 H15">
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4240,7 +5013,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4711,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="str">
-        <f t="shared" ref="I16:I18" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I16:I20" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4771,6 +5544,66 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4785,11 +5618,79 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G14 G16 G18">
-    <cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G14 G16 G18">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H14 H16 H18">
+    <cfRule type="containsText" dxfId="50" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H14 H16 H18">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15 G17">
+    <cfRule type="containsText" dxfId="49" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15 G17">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
+    <cfRule type="containsText" dxfId="48" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4801,12 +5702,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H14 H16 H18">
-    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H14 H16 H18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4818,12 +5719,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15 G17">
-    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17 G15">
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4835,12 +5736,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15 H17">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17 H15">
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4860,7 +5761,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5331,7 +6232,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="str">
-        <f t="shared" ref="I16:I18" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I16:I20" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5391,6 +6292,66 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5405,11 +6366,79 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G14 G16 G18">
-    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G14 G16 G18">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H14 H16 H18">
+    <cfRule type="containsText" dxfId="46" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H14 H16 H18">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15 G17">
+    <cfRule type="containsText" dxfId="45" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15 G17">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
+    <cfRule type="containsText" dxfId="44" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5421,12 +6450,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H14 H16 H18">
-    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H14 H16 H18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5438,12 +6467,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15 G17">
-    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17 G15">
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5455,12 +6484,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15 H17">
-    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17 H15">
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5480,7 +6509,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5951,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="str">
-        <f t="shared" ref="I16:I18" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I16:I20" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6011,6 +7040,66 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6025,11 +7114,79 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G3:G14">
-    <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G14">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H14">
+    <cfRule type="containsText" dxfId="42" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H14">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15:G18">
+    <cfRule type="containsText" dxfId="41" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15:G18">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15:H18">
+    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15:H18">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6041,12 +7198,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H14">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H14">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6058,12 +7215,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15:G18">
-    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15:G18">
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6075,12 +7232,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15:H18">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15:H18">
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6573,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="str">
-        <f t="shared" ref="I16:I18" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I16:I20" si="1">IF(OR(AND(G16&gt;1,G16&lt;&gt;"-"),AND(H16&gt;1,H16&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6633,6 +7790,66 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6651,11 +7868,79 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G14 G16 G18">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G14 G16 G18">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H14 H16 H18">
+    <cfRule type="containsText" dxfId="38" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H14 H16 H18">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15 G17">
+    <cfRule type="containsText" dxfId="37" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15 G17">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
+    <cfRule type="containsText" dxfId="36" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H17">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6667,12 +7952,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H14 H16 H18">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H14 H16 H18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6684,12 +7969,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15 G17">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17 G15">
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6701,12 +7986,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15 H17">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17 H15">
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
